--- a/results/Int Task Remove ACC -0.0/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_7_permute.xlsx
@@ -440,357 +440,357 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.478822105239777</v>
+        <v>0.4969020012882877</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4771539948024255</v>
+        <v>0.4969020012882877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4824870615934785</v>
+        <v>0.4901607027831456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4887180426911886</v>
+        <v>0.4865840385597832</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4784539437151551</v>
+        <v>0.4851513738033362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4916128029141956</v>
+        <v>0.4928688834099643</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5015087403656071</v>
+        <v>0.4928688834099643</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4816135803291797</v>
+        <v>0.5073276915217343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4815547189089536</v>
+        <v>0.4968920059527776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4851902445525421</v>
+        <v>0.5029514004575643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4817018724595189</v>
+        <v>0.4881932875769086</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4906066058061793</v>
+        <v>0.5021467759490016</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.518283134537216</v>
+        <v>0.5065674907265498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5213250483107883</v>
+        <v>0.5111303613869084</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5402634326203327</v>
+        <v>0.5155066524510784</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5512682970169477</v>
+        <v>0.5155066524510784</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5486434108527132</v>
+        <v>0.5059444481464206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5486434108527132</v>
+        <v>0.5320411585704449</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5511505741764954</v>
+        <v>0.5261144799093757</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5569350969547544</v>
+        <v>0.5261144799093757</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5608404966571156</v>
+        <v>0.5222923746695987</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5611986628462273</v>
+        <v>0.5329635059194598</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5524166500077741</v>
+        <v>0.5144227138446502</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5552325581395349</v>
+        <v>0.51189111747851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.570226116701095</v>
+        <v>0.5111403567224184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.554266342373559</v>
+        <v>0.4859076875236001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5474906154905489</v>
+        <v>0.4894843517469625</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5474906154905489</v>
+        <v>0.5138390973101441</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5559588858532685</v>
+        <v>0.5435807734168498</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5252654316874348</v>
+        <v>0.5640451122809356</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5253392861109261</v>
+        <v>0.5620482663645854</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.530647919859621</v>
+        <v>0.4654977677084028</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5296322827125119</v>
+        <v>0.4662141000866262</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5272134115190689</v>
+        <v>0.4644232691410675</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.51760733879745</v>
+        <v>0.4411918882299372</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.514231691877124</v>
+        <v>0.457946847026943</v>
       </c>
     </row>
     <row r="38">
@@ -800,107 +800,107 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5138440949778993</v>
+        <v>0.4552336687323693</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.513701939095089</v>
+        <v>0.4807067812798472</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.442011505741765</v>
+        <v>0.4920109504453477</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4370071744297106</v>
+        <v>0.4454210257435419</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4259873170298305</v>
+        <v>0.447388440949779</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4035711112591902</v>
+        <v>0.387718509140179</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3672591679438484</v>
+        <v>0.392114235578952</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3923596765953666</v>
+        <v>0.3976288842984385</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3761589036227538</v>
+        <v>0.4047677750383155</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3862658537127118</v>
+        <v>0.4568084893716266</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3890084627173985</v>
+        <v>0.4923696719308767</v>
       </c>
     </row>
     <row r="49">
@@ -910,417 +910,417 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4266492303591657</v>
+        <v>0.4917810577286155</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4295684236245307</v>
+        <v>0.4951272739388285</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4167338575331512</v>
+        <v>0.4949945580951112</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3850292085915462</v>
+        <v>0.4949945580951112</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3650457564247795</v>
+        <v>0.4929094200484219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3650457564247795</v>
+        <v>0.5182403767130894</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3640006885675574</v>
+        <v>0.5190794295995202</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3655566291286289</v>
+        <v>0.4573393527464961</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4176317718398081</v>
+        <v>0.4565052975278203</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4168860087514715</v>
+        <v>0.4495568734590524</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3703255147597788</v>
+        <v>0.4467853890406699</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3940622154105862</v>
+        <v>0.4558961373581218</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3970647031385354</v>
+        <v>0.4541691655005442</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4092273605650696</v>
+        <v>0.4649335865484996</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3541103040803181</v>
+        <v>0.4558128428955376</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3607338797450079</v>
+        <v>0.4533551009528887</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4135203571666556</v>
+        <v>0.4495624264232247</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4160569512005509</v>
+        <v>0.4274005464116746</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3802458852535484</v>
+        <v>0.4274005464116746</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.3826791941538393</v>
+        <v>0.4383854201372693</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3782834677150663</v>
+        <v>0.4821394460362942</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4237106017191977</v>
+        <v>0.4585843273139202</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4261977743719597</v>
+        <v>0.4293041025299305</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4261977743719597</v>
+        <v>0.443522467293041</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4269729681704093</v>
+        <v>0.4677694853512805</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4218703493925057</v>
+        <v>0.4774055440794296</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4246473867750605</v>
+        <v>0.4470258323893294</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.430137602452189</v>
+        <v>0.4504309100197685</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4304074765109616</v>
+        <v>0.3598526243308678</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4355100952888652</v>
+        <v>0.3585721107927411</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5360354056995624</v>
+        <v>0.3571294507007841</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5386247528930943</v>
+        <v>0.358051798049799</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5503853757135559</v>
+        <v>0.3580812287599121</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5420742542369117</v>
+        <v>0.3650035538970703</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5488988472046379</v>
+        <v>0.3528808778125764</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5404988783012372</v>
+        <v>0.3881827369449812</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5308522689411608</v>
+        <v>0.4201478199062659</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5337225961218098</v>
+        <v>0.4115812620776971</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5337225961218098</v>
+        <v>0.4778553341773839</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5300770751427112</v>
+        <v>0.484704360187468</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5296311721196775</v>
+        <v>0.4841051953532796</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5042818906732414</v>
+        <v>0.4905172030830057</v>
       </c>
     </row>
   </sheetData>
